--- a/inp_Excel/ana_mezzi_modelli.xlsx
+++ b/inp_Excel/ana_mezzi_modelli.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t>MEZZO_MODELLO_ID</t>
   </si>
@@ -134,6 +134,9 @@
     <t>480 RR RACE EDITION</t>
   </si>
   <si>
+    <t>TT 600 RE</t>
+  </si>
+  <si>
     <t>HILUX</t>
   </si>
   <si>
@@ -276,6 +279,9 @@
   </si>
   <si>
     <t>AFRICA TWIN CRF1100L ADVENTURE SPORTS</t>
+  </si>
+  <si>
+    <t>RS 650 R</t>
   </si>
   <si>
     <t>GRAND CHEROKEE</t>
@@ -510,8 +516,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:D133" totalsRowShown="0" headerRowCount="1">
-  <autoFilter ref="A1:D133"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:D135" totalsRowShown="0" headerRowCount="1">
+  <autoFilter ref="A1:D135"/>
   <tableColumns count="4">
     <tableColumn id="1" name="MEZZO_MODELLO_ID"/>
     <tableColumn id="2" name="MEZZO_MODELLO_DESCRIZIONE"/>
@@ -1065,27 +1071,27 @@
     </row>
     <row r="39" customHeight="1" ht="20">
       <c r="A39" s="5" t="n">
-        <v>1</v>
+        <v>421</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" customHeight="1" ht="20">
       <c r="A40" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>4</v>
@@ -1093,7 +1099,7 @@
     </row>
     <row r="41" customHeight="1" ht="20">
       <c r="A41" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>43</v>
@@ -1107,13 +1113,13 @@
     </row>
     <row r="42" customHeight="1" ht="20">
       <c r="A42" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>4</v>
@@ -1121,13 +1127,13 @@
     </row>
     <row r="43" customHeight="1" ht="20">
       <c r="A43" s="5" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>4</v>
@@ -1135,13 +1141,13 @@
     </row>
     <row r="44" customHeight="1" ht="20">
       <c r="A44" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>4</v>
@@ -1149,7 +1155,7 @@
     </row>
     <row r="45" customHeight="1" ht="20">
       <c r="A45" s="5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>47</v>
@@ -1163,13 +1169,13 @@
     </row>
     <row r="46" customHeight="1" ht="20">
       <c r="A46" s="5" t="n">
-        <v>141</v>
+        <v>38</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>4</v>
@@ -1177,35 +1183,35 @@
     </row>
     <row r="47" customHeight="1" ht="20">
       <c r="A47" s="5" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" customHeight="1" ht="20">
       <c r="A48" s="5" t="n">
-        <v>261</v>
+        <v>161</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" customHeight="1" ht="20">
       <c r="A49" s="5" t="n">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>51</v>
@@ -1219,21 +1225,21 @@
     </row>
     <row r="50" customHeight="1" ht="20">
       <c r="A50" s="5" t="n">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" customHeight="1" ht="20">
       <c r="A51" s="5" t="n">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>53</v>
@@ -1247,7 +1253,7 @@
     </row>
     <row r="52" customHeight="1" ht="20">
       <c r="A52" s="5" t="n">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>54</v>
@@ -1261,13 +1267,13 @@
     </row>
     <row r="53" customHeight="1" ht="20">
       <c r="A53" s="5" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>2</v>
@@ -1275,13 +1281,13 @@
     </row>
     <row r="54" customHeight="1" ht="20">
       <c r="A54" s="5" t="n">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>2</v>
@@ -1289,13 +1295,13 @@
     </row>
     <row r="55" customHeight="1" ht="20">
       <c r="A55" s="5" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>2</v>
@@ -1303,13 +1309,13 @@
     </row>
     <row r="56" customHeight="1" ht="20">
       <c r="A56" s="5" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>2</v>
@@ -1317,7 +1323,7 @@
     </row>
     <row r="57" customHeight="1" ht="20">
       <c r="A57" s="5" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>59</v>
@@ -1331,7 +1337,7 @@
     </row>
     <row r="58" customHeight="1" ht="20">
       <c r="A58" s="5" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>60</v>
@@ -1345,7 +1351,7 @@
     </row>
     <row r="59" customHeight="1" ht="20">
       <c r="A59" s="5" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>61</v>
@@ -1359,7 +1365,7 @@
     </row>
     <row r="60" customHeight="1" ht="20">
       <c r="A60" s="5" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>62</v>
@@ -1373,21 +1379,21 @@
     </row>
     <row r="61" customHeight="1" ht="20">
       <c r="A61" s="5" t="n">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" customHeight="1" ht="20">
       <c r="A62" s="5" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>64</v>
@@ -1401,7 +1407,7 @@
     </row>
     <row r="63" customHeight="1" ht="20">
       <c r="A63" s="5" t="n">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>65</v>
@@ -1415,7 +1421,7 @@
     </row>
     <row r="64" customHeight="1" ht="20">
       <c r="A64" s="5" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>66</v>
@@ -1429,7 +1435,7 @@
     </row>
     <row r="65" customHeight="1" ht="20">
       <c r="A65" s="5" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>67</v>
@@ -1443,27 +1449,27 @@
     </row>
     <row r="66" customHeight="1" ht="20">
       <c r="A66" s="5" t="n">
-        <v>6</v>
+        <v>414</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" customHeight="1" ht="20">
       <c r="A67" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>69</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>4</v>
@@ -1471,7 +1477,7 @@
     </row>
     <row r="68" customHeight="1" ht="20">
       <c r="A68" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>70</v>
@@ -1485,13 +1491,13 @@
     </row>
     <row r="69" customHeight="1" ht="20">
       <c r="A69" s="5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>4</v>
@@ -1499,7 +1505,7 @@
     </row>
     <row r="70" customHeight="1" ht="20">
       <c r="A70" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>72</v>
@@ -1513,7 +1519,7 @@
     </row>
     <row r="71" customHeight="1" ht="20">
       <c r="A71" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>73</v>
@@ -1527,13 +1533,13 @@
     </row>
     <row r="72" customHeight="1" ht="20">
       <c r="A72" s="5" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>4</v>
@@ -1541,13 +1547,13 @@
     </row>
     <row r="73" customHeight="1" ht="20">
       <c r="A73" s="5" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>4</v>
@@ -1555,13 +1561,13 @@
     </row>
     <row r="74" customHeight="1" ht="20">
       <c r="A74" s="5" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D74" s="5" t="n">
         <v>4</v>
@@ -1569,35 +1575,35 @@
     </row>
     <row r="75" customHeight="1" ht="20">
       <c r="A75" s="5" t="n">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" customHeight="1" ht="20">
       <c r="A76" s="5" t="n">
-        <v>322</v>
+        <v>201</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" customHeight="1" ht="20">
       <c r="A77" s="5" t="n">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>79</v>
@@ -1611,7 +1617,7 @@
     </row>
     <row r="78" customHeight="1" ht="20">
       <c r="A78" s="5" t="n">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>80</v>
@@ -1620,26 +1626,26 @@
         <v>13</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" customHeight="1" ht="20">
       <c r="A79" s="5" t="n">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" customHeight="1" ht="20">
       <c r="A80" s="5" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>82</v>
@@ -1653,7 +1659,7 @@
     </row>
     <row r="81" customHeight="1" ht="20">
       <c r="A81" s="5" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>83</v>
@@ -1667,7 +1673,7 @@
     </row>
     <row r="82" customHeight="1" ht="20">
       <c r="A82" s="5" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>84</v>
@@ -1681,13 +1687,13 @@
     </row>
     <row r="83" customHeight="1" ht="20">
       <c r="A83" s="5" t="n">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>85</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>2</v>
@@ -1695,7 +1701,7 @@
     </row>
     <row r="84" customHeight="1" ht="20">
       <c r="A84" s="5" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>86</v>
@@ -1709,13 +1715,13 @@
     </row>
     <row r="85" customHeight="1" ht="20">
       <c r="A85" s="5" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>2</v>
@@ -1723,7 +1729,7 @@
     </row>
     <row r="86" customHeight="1" ht="20">
       <c r="A86" s="5" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>88</v>
@@ -1737,41 +1743,41 @@
     </row>
     <row r="87" customHeight="1" ht="20">
       <c r="A87" s="5" t="n">
-        <v>9</v>
+        <v>368</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>89</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" customHeight="1" ht="20">
       <c r="A88" s="5" t="n">
-        <v>12</v>
+        <v>422</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" customHeight="1" ht="20">
       <c r="A89" s="5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>91</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>4</v>
@@ -1779,7 +1785,7 @@
     </row>
     <row r="90" customHeight="1" ht="20">
       <c r="A90" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>92</v>
@@ -1793,13 +1799,13 @@
     </row>
     <row r="91" customHeight="1" ht="20">
       <c r="A91" s="5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>93</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D91" s="5" t="n">
         <v>4</v>
@@ -1807,13 +1813,13 @@
     </row>
     <row r="92" customHeight="1" ht="20">
       <c r="A92" s="5" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>94</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D92" s="5" t="n">
         <v>4</v>
@@ -1821,13 +1827,13 @@
     </row>
     <row r="93" customHeight="1" ht="20">
       <c r="A93" s="5" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>95</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D93" s="5" t="n">
         <v>4</v>
@@ -1835,13 +1841,13 @@
     </row>
     <row r="94" customHeight="1" ht="20">
       <c r="A94" s="5" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>96</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D94" s="5" t="n">
         <v>4</v>
@@ -1849,7 +1855,7 @@
     </row>
     <row r="95" customHeight="1" ht="20">
       <c r="A95" s="5" t="n">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>97</v>
@@ -1863,7 +1869,7 @@
     </row>
     <row r="96" customHeight="1" ht="20">
       <c r="A96" s="5" t="n">
-        <v>181</v>
+        <v>37</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>98</v>
@@ -1877,7 +1883,7 @@
     </row>
     <row r="97" customHeight="1" ht="20">
       <c r="A97" s="5" t="n">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>99</v>
@@ -1891,35 +1897,35 @@
     </row>
     <row r="98" customHeight="1" ht="20">
       <c r="A98" s="5" t="n">
-        <v>321</v>
+        <v>181</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>100</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" customHeight="1" ht="20">
       <c r="A99" s="5" t="n">
-        <v>326</v>
+        <v>241</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>101</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" customHeight="1" ht="20">
       <c r="A100" s="5" t="n">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>102</v>
@@ -1933,7 +1939,7 @@
     </row>
     <row r="101" customHeight="1" ht="20">
       <c r="A101" s="5" t="n">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>103</v>
@@ -1942,12 +1948,12 @@
         <v>13</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" customHeight="1" ht="20">
       <c r="A102" s="5" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>104</v>
@@ -1956,12 +1962,12 @@
         <v>13</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" customHeight="1" ht="20">
       <c r="A103" s="5" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>105</v>
@@ -1975,7 +1981,7 @@
     </row>
     <row r="104" customHeight="1" ht="20">
       <c r="A104" s="5" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>106</v>
@@ -1989,7 +1995,7 @@
     </row>
     <row r="105" customHeight="1" ht="20">
       <c r="A105" s="5" t="n">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>107</v>
@@ -2003,7 +2009,7 @@
     </row>
     <row r="106" customHeight="1" ht="20">
       <c r="A106" s="5" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>108</v>
@@ -2012,12 +2018,12 @@
         <v>13</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" customHeight="1" ht="20">
       <c r="A107" s="5" t="n">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>109</v>
@@ -2026,12 +2032,12 @@
         <v>13</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" customHeight="1" ht="20">
       <c r="A108" s="5" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>110</v>
@@ -2045,7 +2051,7 @@
     </row>
     <row r="109" customHeight="1" ht="20">
       <c r="A109" s="5" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>111</v>
@@ -2059,7 +2065,7 @@
     </row>
     <row r="110" customHeight="1" ht="20">
       <c r="A110" s="5" t="n">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>112</v>
@@ -2073,41 +2079,41 @@
     </row>
     <row r="111" customHeight="1" ht="20">
       <c r="A111" s="5" t="n">
-        <v>3</v>
+        <v>345</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>113</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" customHeight="1" ht="20">
       <c r="A112" s="5" t="n">
-        <v>8</v>
+        <v>347</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>114</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" customHeight="1" ht="20">
       <c r="A113" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113" s="5" t="n">
         <v>4</v>
@@ -2115,13 +2121,13 @@
     </row>
     <row r="114" customHeight="1" ht="20">
       <c r="A114" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>116</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D114" s="5" t="n">
         <v>4</v>
@@ -2129,7 +2135,7 @@
     </row>
     <row r="115" customHeight="1" ht="20">
       <c r="A115" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>117</v>
@@ -2143,13 +2149,13 @@
     </row>
     <row r="116" customHeight="1" ht="20">
       <c r="A116" s="5" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>118</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D116" s="5" t="n">
         <v>4</v>
@@ -2157,13 +2163,13 @@
     </row>
     <row r="117" customHeight="1" ht="20">
       <c r="A117" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>119</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>4</v>
@@ -2171,13 +2177,13 @@
     </row>
     <row r="118" customHeight="1" ht="20">
       <c r="A118" s="5" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D118" s="5" t="n">
         <v>4</v>
@@ -2185,55 +2191,55 @@
     </row>
     <row r="119" customHeight="1" ht="20">
       <c r="A119" s="5" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>121</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="20">
       <c r="A120" s="5" t="n">
-        <v>337</v>
+        <v>34</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>122</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="20">
       <c r="A121" s="5" t="n">
-        <v>350</v>
+        <v>42</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>123</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" customHeight="1" ht="20">
       <c r="A122" s="5" t="n">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>124</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D122" s="5" t="n">
         <v>2</v>
@@ -2241,7 +2247,7 @@
     </row>
     <row r="123" customHeight="1" ht="20">
       <c r="A123" s="5" t="n">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>125</v>
@@ -2255,13 +2261,13 @@
     </row>
     <row r="124" customHeight="1" ht="20">
       <c r="A124" s="5" t="n">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D124" s="5" t="n">
         <v>2</v>
@@ -2269,13 +2275,13 @@
     </row>
     <row r="125" customHeight="1" ht="20">
       <c r="A125" s="5" t="n">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>127</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>2</v>
@@ -2283,27 +2289,27 @@
     </row>
     <row r="126" customHeight="1" ht="20">
       <c r="A126" s="5" t="n">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" customHeight="1" ht="20">
       <c r="A127" s="5" t="n">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>129</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D127" s="5" t="n">
         <v>2</v>
@@ -2311,27 +2317,27 @@
     </row>
     <row r="128" customHeight="1" ht="20">
       <c r="A128" s="5" t="n">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>130</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" customHeight="1" ht="20">
       <c r="A129" s="5" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>131</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D129" s="5" t="n">
         <v>2</v>
@@ -2339,13 +2345,13 @@
     </row>
     <row r="130" customHeight="1" ht="20">
       <c r="A130" s="5" t="n">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>132</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D130" s="5" t="n">
         <v>2</v>
@@ -2353,13 +2359,13 @@
     </row>
     <row r="131" customHeight="1" ht="20">
       <c r="A131" s="5" t="n">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>133</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="D131" s="5" t="n">
         <v>2</v>
@@ -2367,13 +2373,13 @@
     </row>
     <row r="132" customHeight="1" ht="20">
       <c r="A132" s="5" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>134</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="D132" s="5" t="n">
         <v>2</v>
@@ -2381,7 +2387,7 @@
     </row>
     <row r="133" customHeight="1" ht="20">
       <c r="A133" s="5" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>135</v>
@@ -2390,6 +2396,34 @@
         <v>11</v>
       </c>
       <c r="D133" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" ht="20">
+      <c r="A134" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" ht="20">
+      <c r="A135" s="5" t="n">
+        <v>383</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D135" s="5" t="n">
         <v>2</v>
       </c>
     </row>
